--- a/ex6/brtt-documentation/BRTT_result_spreadsheet - B.xlsx
+++ b/ex6/brtt-documentation/BRTT_result_spreadsheet - B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saavim\TTK4147 sanntid\TTK4147_Sanntidsystemer\ex6\brtt-documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F948E088-606B-4DAF-B52B-CFA06168DDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79002FCC-933C-49AF-AC62-0BBD9CB4C94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="1" r:id="rId1"/>
@@ -698,9 +698,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -708,6 +705,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -828,64 +828,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -897,34 +897,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>483</c:v>
+                  <c:v>401</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>131</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>143</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -993,64 +993,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1062,34 +1062,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>478</c:v>
+                  <c:v>406</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>108</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>160</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>93</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38</c:v>
+                  <c:v>85</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -1158,64 +1158,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1227,34 +1227,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>454</c:v>
+                  <c:v>381</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>118</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>147</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>171</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>82</c:v>
+                  <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>28</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -1467,64 +1467,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1536,43 +1536,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>715</c:v>
+                  <c:v>620</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>175</c:v>
+                  <c:v>126</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>76</c:v>
+                  <c:v>101</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -1632,64 +1632,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1701,43 +1701,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>714</c:v>
+                  <c:v>625</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>151</c:v>
+                  <c:v>105</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>80</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -1797,64 +1797,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1866,46 +1866,46 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>720</c:v>
+                  <c:v>620</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>154</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>71</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>16</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -2116,64 +2116,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2185,34 +2185,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>488</c:v>
+                  <c:v>415</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>134</c:v>
+                  <c:v>89</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>138</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>115</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>104</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>21</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -2281,64 +2281,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2350,34 +2350,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>525</c:v>
+                  <c:v>458</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>133</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>127</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>106</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>89</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -2404,7 +2404,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -2446,64 +2446,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2551,31 +2551,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>54</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>54</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>157</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>110</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>209</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>345</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2765,64 +2765,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2834,34 +2834,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>356</c:v>
+                  <c:v>189</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>335</c:v>
+                  <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>213</c:v>
+                  <c:v>184</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>40</c:v>
+                  <c:v>186</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -2930,64 +2930,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2999,31 +2999,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>349</c:v>
+                  <c:v>203</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>343</c:v>
+                  <c:v>186</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>205</c:v>
+                  <c:v>191</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>62</c:v>
+                  <c:v>173</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>41</c:v>
+                  <c:v>129</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -3095,64 +3095,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3185,13 +3185,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>237</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>397</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>366</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -3203,22 +3203,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>133</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>223</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>218</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -3414,64 +3414,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3483,58 +3483,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>351</c:v>
+                  <c:v>206</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>289</c:v>
+                  <c:v>182</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>170</c:v>
+                  <c:v>149</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28</c:v>
+                  <c:v>153</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24</c:v>
+                  <c:v>108</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>32</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>29</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -3579,64 +3579,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3648,58 +3648,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>331</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>293</c:v>
+                  <c:v>179</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>192</c:v>
+                  <c:v>161</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28</c:v>
+                  <c:v>166</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30</c:v>
+                  <c:v>129</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>29</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>26</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>27</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -3744,64 +3744,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3834,43 +3834,43 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>392</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>390</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>214</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>237</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>213</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -4063,64 +4063,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4132,19 +4132,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>399</c:v>
+                  <c:v>215</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>372</c:v>
+                  <c:v>221</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>229</c:v>
+                  <c:v>193</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>166</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -4228,64 +4228,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4297,19 +4297,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>388</c:v>
+                  <c:v>226</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>390</c:v>
+                  <c:v>196</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>222</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>215</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>141</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -4393,64 +4393,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4483,16 +4483,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>359</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>399</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>236</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -4504,22 +4504,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>201</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>217</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>231</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -4698,64 +4698,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4767,34 +4767,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>1415</c:v>
+                  <c:v>1188</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>349</c:v>
+                  <c:v>275</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>401</c:v>
+                  <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>474</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>265</c:v>
+                  <c:v>234</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>96</c:v>
+                  <c:v>248</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>276</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>159</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>146</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -4863,64 +4863,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4932,46 +4932,46 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>2149</c:v>
+                  <c:v>1865</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>480</c:v>
+                  <c:v>349</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>227</c:v>
+                  <c:v>296</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>44</c:v>
+                  <c:v>176</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>53</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>42</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -5028,64 +5028,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5097,34 +5097,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>1013</c:v>
+                  <c:v>873</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>267</c:v>
+                  <c:v>172</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>265</c:v>
+                  <c:v>148</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>221</c:v>
+                  <c:v>154</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>193</c:v>
+                  <c:v>143</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>111</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>123</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>98</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -5133,31 +5133,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>54</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>54</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>157</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>110</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>209</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>345</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5193,64 +5193,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5262,34 +5262,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>705</c:v>
+                  <c:v>392</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>678</c:v>
+                  <c:v>391</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>418</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>102</c:v>
+                  <c:v>359</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>96</c:v>
+                  <c:v>249</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>237</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>397</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>366</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -5301,22 +5301,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>133</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>223</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>218</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -5358,64 +5358,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5427,64 +5427,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>682</c:v>
+                  <c:v>381</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>582</c:v>
+                  <c:v>361</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>362</c:v>
+                  <c:v>310</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>56</c:v>
+                  <c:v>319</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54</c:v>
+                  <c:v>237</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>61</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>55</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>442</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>453</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>249</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>262</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>234</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>111</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -5523,64 +5523,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1200</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1600</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2400</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2800</c:v>
+                  <c:v>1540</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3600</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4000</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3080</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3520</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3740</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4180</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5592,19 +5592,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>787</c:v>
+                  <c:v>441</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>762</c:v>
+                  <c:v>417</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>451</c:v>
+                  <c:v>415</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>307</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5613,16 +5613,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>359</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>399</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>236</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -5634,22 +5634,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>201</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>217</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>231</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -6289,80 +6289,80 @@
   </cols>
   <sheetData>
     <row r="2" spans="5:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="J2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="O2" s="3" t="s">
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="O2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="T2" s="3" t="s">
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="T2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="Y2" s="3" t="s">
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="Y2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AD2" s="3" t="s">
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AD2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
     </row>
     <row r="3" spans="5:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="6"/>
-      <c r="J3" s="4" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="J3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-      <c r="O3" s="4" t="s">
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="5"/>
+      <c r="O3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="6"/>
-      <c r="T3" s="4" t="s">
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5"/>
+      <c r="T3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="6"/>
-      <c r="Y3" s="4" t="s">
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="5"/>
+      <c r="Y3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="6"/>
-      <c r="AD3" s="4" t="s">
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="5"/>
+      <c r="AD3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AE3" s="5"/>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="6"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="5"/>
     </row>
     <row r="5" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
@@ -80796,18 +80796,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="T2:W2"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="Y3:AB3"/>
+    <mergeCell ref="AD2:AG2"/>
+    <mergeCell ref="AD3:AG3"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="O2:R2"/>
     <mergeCell ref="O3:R3"/>
-    <mergeCell ref="T2:W2"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="Y2:AB2"/>
-    <mergeCell ref="Y3:AB3"/>
-    <mergeCell ref="AD2:AG2"/>
-    <mergeCell ref="AD3:AG3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -80823,86 +80823,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="J2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="O2" s="3" t="s">
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="O2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="T2" s="3" t="s">
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="T2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="Y2" s="3" t="s">
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="Y2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AD2" s="3" t="s">
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AD2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
     </row>
     <row r="3" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="4" t="str">
+      <c r="E3" s="3" t="str">
         <f>Input!E3</f>
         <v>Task B no yield</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="6"/>
-      <c r="J3" s="4" t="str">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="J3" s="3" t="str">
         <f>Input!J3</f>
         <v>Task B yield</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-      <c r="O3" s="4" t="str">
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="5"/>
+      <c r="O3" s="3" t="str">
         <f>Input!O3</f>
         <v>Task C yield</v>
       </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="6"/>
-      <c r="T3" s="4" t="str">
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5"/>
+      <c r="T3" s="3" t="str">
         <f>Input!T3</f>
         <v>Task D yield</v>
       </c>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="6"/>
-      <c r="Y3" s="4" t="str">
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="5"/>
+      <c r="Y3" s="3" t="str">
         <f>Input!Y3</f>
         <v>Task E: 1, 2, 3</v>
       </c>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="6"/>
-      <c r="AD3" s="4" t="str">
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="5"/>
+      <c r="AD3" s="3" t="str">
         <f>Input!AD3</f>
         <v>Task E: 3, 2, 1</v>
       </c>
-      <c r="AE3" s="5"/>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="6"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="5"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="E5" s="1" t="s">
@@ -81290,43 +81290,43 @@
       </c>
       <c r="E10">
         <f t="array" ref="E10:E30">FREQUENCY(Input!F13:F1012,Calculations!$B$10:$B$30)</f>
-        <v>483</v>
+        <v>401</v>
       </c>
       <c r="F10">
         <f t="array" ref="F10:F30">FREQUENCY(Input!G13:G1012,Calculations!$B$10:$B$30)</f>
-        <v>478</v>
+        <v>406</v>
       </c>
       <c r="G10">
         <f t="array" ref="G10:G30">FREQUENCY(Input!H13:H1012,Calculations!$B$10:$B$30)</f>
-        <v>454</v>
+        <v>381</v>
       </c>
       <c r="H10">
         <f>E10+F10+G10</f>
-        <v>1415</v>
+        <v>1188</v>
       </c>
       <c r="J10">
         <f t="array" ref="J10:J30">FREQUENCY(Input!K13:K1012,Calculations!$B$10:$B$30)</f>
-        <v>715</v>
+        <v>620</v>
       </c>
       <c r="K10">
         <f t="array" ref="K10:K30">FREQUENCY(Input!L13:L1012,Calculations!$B$10:$B$30)</f>
-        <v>714</v>
+        <v>625</v>
       </c>
       <c r="L10">
         <f t="array" ref="L10:L30">FREQUENCY(Input!M13:M1012,Calculations!$B$10:$B$30)</f>
-        <v>720</v>
+        <v>620</v>
       </c>
       <c r="M10">
         <f>J10+K10+L10</f>
-        <v>2149</v>
+        <v>1865</v>
       </c>
       <c r="O10">
         <f t="array" ref="O10:O30">FREQUENCY(Input!P13:P1012,Calculations!$B$10:$B$30)</f>
-        <v>488</v>
+        <v>415</v>
       </c>
       <c r="P10">
         <f t="array" ref="P10:P30">FREQUENCY(Input!Q13:Q1012,Calculations!$B$10:$B$30)</f>
-        <v>525</v>
+        <v>458</v>
       </c>
       <c r="Q10">
         <f t="array" ref="Q10:Q30">FREQUENCY(Input!R13:R1012,Calculations!$B$10:$B$30)</f>
@@ -81334,15 +81334,15 @@
       </c>
       <c r="R10">
         <f>O10+P10+Q10</f>
-        <v>1013</v>
+        <v>873</v>
       </c>
       <c r="T10">
         <f t="array" ref="T10:T30">FREQUENCY(Input!U13:U1012,Calculations!$B$10:$B$30)</f>
-        <v>356</v>
+        <v>189</v>
       </c>
       <c r="U10">
         <f t="array" ref="U10:U30">FREQUENCY(Input!V13:V1012,Calculations!$B$10:$B$30)</f>
-        <v>349</v>
+        <v>203</v>
       </c>
       <c r="V10">
         <f t="array" ref="V10:V30">FREQUENCY(Input!W13:W1012,Calculations!$B$10:$B$30)</f>
@@ -81350,15 +81350,15 @@
       </c>
       <c r="W10">
         <f>T10+U10+V10</f>
-        <v>705</v>
+        <v>392</v>
       </c>
       <c r="Y10">
         <f t="array" ref="Y10:Y30">FREQUENCY(Input!Z13:Z1012,Calculations!$B$10:$B$30)</f>
-        <v>351</v>
+        <v>206</v>
       </c>
       <c r="Z10">
         <f t="array" ref="Z10:Z30">FREQUENCY(Input!AA13:AA1012,Calculations!$B$10:$B$30)</f>
-        <v>331</v>
+        <v>175</v>
       </c>
       <c r="AA10">
         <f t="array" ref="AA10:AA30">FREQUENCY(Input!AB13:AB1012,Calculations!$B$10:$B$30)</f>
@@ -81366,15 +81366,15 @@
       </c>
       <c r="AB10">
         <f>Y10+Z10+AA10</f>
-        <v>682</v>
+        <v>381</v>
       </c>
       <c r="AD10">
         <f t="array" ref="AD10:AD30">FREQUENCY(Input!AE13:AE1012,Calculations!$B$10:$B$30)</f>
-        <v>399</v>
+        <v>215</v>
       </c>
       <c r="AE10">
         <f t="array" ref="AE10:AE30">FREQUENCY(Input!AF13:AF1012,Calculations!$B$10:$B$30)</f>
-        <v>388</v>
+        <v>226</v>
       </c>
       <c r="AF10">
         <f t="array" ref="AF10:AF30">FREQUENCY(Input!AG13:AG1012,Calculations!$B$10:$B$30)</f>
@@ -81382,7 +81382,7 @@
       </c>
       <c r="AG10">
         <f>AD10+AE10+AF10</f>
-        <v>787</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -81391,89 +81391,89 @@
       </c>
       <c r="B11">
         <f>A11*Graphs!$D$2</f>
-        <v>400</v>
+        <v>220</v>
       </c>
       <c r="D11">
         <f>B11</f>
-        <v>400</v>
+        <v>220</v>
       </c>
       <c r="E11">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="G11">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="H11">
         <f t="shared" ref="H11:H30" si="0">E11+F11+G11</f>
-        <v>349</v>
+        <v>275</v>
       </c>
       <c r="J11">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="K11">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="L11">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="M11">
         <f t="shared" ref="M11:M30" si="1">J11+K11+L11</f>
-        <v>480</v>
+        <v>349</v>
       </c>
       <c r="O11">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="P11">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
         <f t="shared" ref="R11:R30" si="2">O11+P11+Q11</f>
-        <v>267</v>
+        <v>172</v>
       </c>
       <c r="T11">
-        <v>335</v>
+        <v>205</v>
       </c>
       <c r="U11">
-        <v>343</v>
+        <v>186</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
         <f t="shared" ref="W11:W30" si="3">T11+U11+V11</f>
-        <v>678</v>
+        <v>391</v>
       </c>
       <c r="Y11">
-        <v>289</v>
+        <v>182</v>
       </c>
       <c r="Z11">
-        <v>293</v>
+        <v>179</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
         <f t="shared" ref="AB11:AB30" si="4">Y11+Z11+AA11</f>
-        <v>582</v>
+        <v>361</v>
       </c>
       <c r="AD11">
-        <v>372</v>
+        <v>221</v>
       </c>
       <c r="AE11">
-        <v>390</v>
+        <v>196</v>
       </c>
       <c r="AF11">
         <v>0</v>
       </c>
       <c r="AG11">
         <f t="shared" ref="AG11:AG30" si="5">AD11+AE11+AF11</f>
-        <v>762</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -81482,79 +81482,79 @@
       </c>
       <c r="B12">
         <f>A12*Graphs!$D$2</f>
-        <v>800</v>
+        <v>440</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D30" si="6">B12</f>
-        <v>800</v>
+        <v>440</v>
       </c>
       <c r="E12">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="F12">
-        <v>123</v>
+        <v>64</v>
       </c>
       <c r="G12">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="H12">
         <f t="shared" si="0"/>
-        <v>401</v>
+        <v>205</v>
       </c>
       <c r="J12">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="K12">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="L12">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <f t="shared" si="1"/>
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="O12">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="P12">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="Q12">
         <v>0</v>
       </c>
       <c r="R12">
         <f t="shared" si="2"/>
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="T12">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="U12">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
         <f t="shared" si="3"/>
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="Y12">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="Z12">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
         <f t="shared" si="4"/>
-        <v>362</v>
+        <v>310</v>
       </c>
       <c r="AD12">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="AE12">
         <v>222</v>
@@ -81564,7 +81564,7 @@
       </c>
       <c r="AG12">
         <f t="shared" si="5"/>
-        <v>451</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -81573,89 +81573,89 @@
       </c>
       <c r="B13">
         <f>A13*Graphs!$D$2</f>
-        <v>1200</v>
+        <v>660</v>
       </c>
       <c r="D13">
         <f t="shared" si="6"/>
-        <v>1200</v>
+        <v>660</v>
       </c>
       <c r="E13">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="F13">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="G13">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
-        <v>474</v>
+        <v>150</v>
       </c>
       <c r="J13">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="K13">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="L13">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="M13">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="O13">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="P13">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="Q13">
         <v>0</v>
       </c>
       <c r="R13">
         <f t="shared" si="2"/>
-        <v>221</v>
+        <v>154</v>
       </c>
       <c r="T13">
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="U13">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
         <f t="shared" si="3"/>
-        <v>102</v>
+        <v>359</v>
       </c>
       <c r="Y13">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="Z13">
-        <v>28</v>
+        <v>166</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
         <f t="shared" si="4"/>
-        <v>56</v>
+        <v>319</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="AF13">
         <v>0</v>
       </c>
       <c r="AG13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -81664,89 +81664,89 @@
       </c>
       <c r="B14">
         <f>A14*Graphs!$D$2</f>
-        <v>1600</v>
+        <v>880</v>
       </c>
       <c r="D14">
         <f t="shared" si="6"/>
-        <v>1600</v>
+        <v>880</v>
       </c>
       <c r="E14">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F14">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="G14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="J14">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="K14">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="L14">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="M14">
         <f t="shared" si="1"/>
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="O14">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="P14">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="Q14">
         <v>0</v>
       </c>
       <c r="R14">
         <f t="shared" si="2"/>
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="T14">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="U14">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
         <f t="shared" si="3"/>
-        <v>96</v>
+        <v>249</v>
       </c>
       <c r="Y14">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="Z14">
-        <v>30</v>
+        <v>129</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
         <f t="shared" si="4"/>
-        <v>54</v>
+        <v>237</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="AF14">
         <v>0</v>
       </c>
       <c r="AG14">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -81755,76 +81755,76 @@
       </c>
       <c r="B15">
         <f>A15*Graphs!$D$2</f>
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="D15">
         <f t="shared" si="6"/>
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F15">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="G15">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="H15">
         <f t="shared" si="0"/>
-        <v>96</v>
+        <v>248</v>
       </c>
       <c r="J15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L15">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="O15">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="P15">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="Q15">
         <v>0</v>
       </c>
       <c r="R15">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="T15">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="Y15">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="Z15">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
         <f t="shared" si="4"/>
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -81846,76 +81846,76 @@
       </c>
       <c r="B16">
         <f>A16*Graphs!$D$2</f>
-        <v>2400</v>
+        <v>1320</v>
       </c>
       <c r="D16">
         <f t="shared" si="6"/>
-        <v>2400</v>
+        <v>1320</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Y16">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="Z16">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
         <f t="shared" si="4"/>
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -81937,76 +81937,76 @@
       </c>
       <c r="B17">
         <f>A17*Graphs!$D$2</f>
-        <v>2800</v>
+        <v>1540</v>
       </c>
       <c r="D17">
         <f t="shared" si="6"/>
-        <v>2800</v>
+        <v>1540</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q17">
         <v>0</v>
       </c>
       <c r="R17">
         <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+      <c r="T17">
+        <v>29</v>
+      </c>
+      <c r="U17">
+        <v>22</v>
+      </c>
+      <c r="V17">
         <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>237</v>
       </c>
       <c r="W17">
         <f t="shared" si="3"/>
-        <v>237</v>
+        <v>51</v>
       </c>
       <c r="Y17">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Z17">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AA17">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="AB17">
         <f t="shared" si="4"/>
-        <v>442</v>
+        <v>33</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -82015,11 +82015,11 @@
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG17">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -82028,76 +82028,76 @@
       </c>
       <c r="B18">
         <f>A18*Graphs!$D$2</f>
-        <v>3200</v>
+        <v>1760</v>
       </c>
       <c r="D18">
         <f t="shared" si="6"/>
-        <v>3200</v>
+        <v>1760</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q18">
         <v>0</v>
       </c>
       <c r="R18">
         <f t="shared" si="2"/>
+        <v>98</v>
+      </c>
+      <c r="T18">
+        <v>31</v>
+      </c>
+      <c r="U18">
+        <v>27</v>
+      </c>
+      <c r="V18">
         <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>397</v>
       </c>
       <c r="W18">
         <f t="shared" si="3"/>
-        <v>397</v>
+        <v>58</v>
       </c>
       <c r="Y18">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Z18">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AA18">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="AB18">
         <f t="shared" si="4"/>
-        <v>453</v>
+        <v>35</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -82106,11 +82106,11 @@
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="AG18">
         <f t="shared" si="5"/>
-        <v>359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -82119,76 +82119,76 @@
       </c>
       <c r="B19">
         <f>A19*Graphs!$D$2</f>
-        <v>3600</v>
+        <v>1980</v>
       </c>
       <c r="D19">
         <f t="shared" si="6"/>
-        <v>3600</v>
+        <v>1980</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H19">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M19">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="Q19">
         <v>0</v>
       </c>
       <c r="R19">
         <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="T19">
         <v>1</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
       </c>
       <c r="U19">
         <v>0</v>
       </c>
       <c r="V19">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="W19">
         <f t="shared" si="3"/>
-        <v>366</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Z19">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA19">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="AB19">
         <f t="shared" si="4"/>
-        <v>249</v>
+        <v>35</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -82197,11 +82197,11 @@
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="AG19">
         <f t="shared" si="5"/>
-        <v>399</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -82210,11 +82210,11 @@
       </c>
       <c r="B20">
         <f>A20*Graphs!$D$2</f>
-        <v>4000</v>
+        <v>2200</v>
       </c>
       <c r="D20">
         <f t="shared" si="6"/>
-        <v>4000</v>
+        <v>2200</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -82230,17 +82230,17 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -82269,17 +82269,17 @@
         <v>0</v>
       </c>
       <c r="Y20">
+        <v>14</v>
+      </c>
+      <c r="Z20">
+        <v>17</v>
+      </c>
+      <c r="AA20">
         <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>4</v>
       </c>
       <c r="AB20">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -82288,11 +82288,11 @@
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="AG20">
         <f t="shared" si="5"/>
-        <v>236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
@@ -82301,11 +82301,11 @@
       </c>
       <c r="B21">
         <f>A21*Graphs!$D$2</f>
-        <v>4400</v>
+        <v>2420</v>
       </c>
       <c r="D21">
         <f t="shared" si="6"/>
-        <v>4400</v>
+        <v>2420</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -82324,14 +82324,14 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -82360,17 +82360,17 @@
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -82392,11 +82392,11 @@
       </c>
       <c r="B22">
         <f>A22*Graphs!$D$2</f>
-        <v>4800</v>
+        <v>2640</v>
       </c>
       <c r="D22">
         <f t="shared" si="6"/>
-        <v>4800</v>
+        <v>2640</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -82412,17 +82412,17 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -82431,11 +82431,11 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R22">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -82451,17 +82451,17 @@
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB22">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -82483,11 +82483,11 @@
       </c>
       <c r="B23">
         <f>A23*Graphs!$D$2</f>
-        <v>5200</v>
+        <v>2860</v>
       </c>
       <c r="D23">
         <f t="shared" si="6"/>
-        <v>5200</v>
+        <v>2860</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -82509,11 +82509,11 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -82522,11 +82522,11 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R23">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -82535,24 +82535,24 @@
         <v>0</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="W23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="AB23">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -82574,11 +82574,11 @@
       </c>
       <c r="B24">
         <f>A24*Graphs!$D$2</f>
-        <v>5600</v>
+        <v>3080</v>
       </c>
       <c r="D24">
         <f t="shared" si="6"/>
-        <v>5600</v>
+        <v>3080</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -82613,11 +82613,11 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R24">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -82626,24 +82626,24 @@
         <v>0</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="W24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="AB24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -82652,11 +82652,11 @@
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AG24">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
@@ -82665,11 +82665,11 @@
       </c>
       <c r="B25">
         <f>A25*Graphs!$D$2</f>
-        <v>6000</v>
+        <v>3300</v>
       </c>
       <c r="D25">
         <f t="shared" si="6"/>
-        <v>6000</v>
+        <v>3300</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -82704,11 +82704,11 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R25">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -82717,24 +82717,24 @@
         <v>0</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="W25">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="AB25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -82743,11 +82743,11 @@
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AG25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
@@ -82756,11 +82756,11 @@
       </c>
       <c r="B26">
         <f>A26*Graphs!$D$2</f>
-        <v>6400</v>
+        <v>3520</v>
       </c>
       <c r="D26">
         <f t="shared" si="6"/>
-        <v>6400</v>
+        <v>3520</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -82795,11 +82795,11 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R26">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -82808,24 +82808,24 @@
         <v>0</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="W26">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="AB26">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -82834,11 +82834,11 @@
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="AG26">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
@@ -82847,11 +82847,11 @@
       </c>
       <c r="B27">
         <f>A27*Graphs!$D$2</f>
-        <v>6800</v>
+        <v>3740</v>
       </c>
       <c r="D27">
         <f t="shared" si="6"/>
-        <v>6800</v>
+        <v>3740</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -82886,11 +82886,11 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="R27">
         <f t="shared" si="2"/>
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="T27">
         <v>0</v>
@@ -82899,24 +82899,24 @@
         <v>0</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="W27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AB27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -82925,11 +82925,11 @@
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="AG27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
@@ -82938,11 +82938,11 @@
       </c>
       <c r="B28">
         <f>A28*Graphs!$D$2</f>
-        <v>7200</v>
+        <v>3960</v>
       </c>
       <c r="D28">
         <f t="shared" si="6"/>
-        <v>7200</v>
+        <v>3960</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -82974,14 +82974,14 @@
         <v>0</v>
       </c>
       <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
         <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>110</v>
       </c>
       <c r="R28">
         <f t="shared" si="2"/>
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="T28">
         <v>0</v>
@@ -82990,11 +82990,11 @@
         <v>0</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W28">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y28">
         <v>0</v>
@@ -83003,11 +83003,11 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD28">
         <v>0</v>
@@ -83016,11 +83016,11 @@
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="AG28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
@@ -83029,11 +83029,11 @@
       </c>
       <c r="B29">
         <f>A29*Graphs!$D$2</f>
-        <v>7600</v>
+        <v>4180</v>
       </c>
       <c r="D29">
         <f t="shared" si="6"/>
-        <v>7600</v>
+        <v>4180</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -83068,11 +83068,11 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="R29">
         <f t="shared" si="2"/>
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="T29">
         <v>0</v>
@@ -83094,11 +83094,11 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB29">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD29">
         <v>0</v>
@@ -83107,11 +83107,11 @@
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AG29">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
@@ -83120,11 +83120,11 @@
       </c>
       <c r="B30">
         <f>A30*Graphs!$D$2</f>
-        <v>8000</v>
+        <v>4400</v>
       </c>
       <c r="D30">
         <f t="shared" si="6"/>
-        <v>8000</v>
+        <v>4400</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -83159,11 +83159,11 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>345</v>
+        <v>1000</v>
       </c>
       <c r="R30">
         <f t="shared" si="2"/>
-        <v>345</v>
+        <v>1000</v>
       </c>
       <c r="T30">
         <v>0</v>
@@ -83276,7 +83276,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2">
-        <v>8000</v>
+        <v>4400</v>
       </c>
     </row>
   </sheetData>
